--- a/stories/arbres/ATOM-SOC.CUI.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Maya entre dans la cuisine. Maman est là. Maya dit : je veux aider. Maman sourit. Maman dit : tu fais une tâche sûre, avec un adulte. Maya ouvre l'eau. Elle lave une tomate. L'eau est froide. La tomate est lisse. Maya pose la tomate. Ensuite, elle prend une cuillère. Elle pose la cuillère près de l'assiette. Puis Maya va au pain. Elle apporte le pain à table. Maman dit : merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Maya reste avec maman.</t>
+          <t>C'est le matin. Maya entre dans la cuisine. Maman est là. Je veux aider. Maman sourit. Tu fais une tâche sûre, avec un adulte. Maya ouvre l'eau. Elle lave une tomate. L'eau est froide. La tomate est lisse. Maya pose la tomate. Ensuite, elle prend une cuillère. Elle pose la cuillère près de l'assiette. Puis Maya va au pain. Elle apporte le pain à table. Merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Maya reste avec maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Maya entre dans la cuisine. Maman est là.
+enfant-f|Je veux aider. Maman sourit.
+maman|Tu fais une tâche sûre, avec un adulte.
+narrateur|Maya ouvre l'eau. Elle lave une tomate. L'eau est froide. La tomate est lisse. Maya pose la tomate. Ensuite, elle prend une cuillère. Elle pose la cuillère près de l'assiette. Puis Maya va au pain. Elle apporte le pain à table.
+maman|Merci. Laver. Poser. Apporter. Ce sont des tâches sûres.
+narrateur|Maya reste avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Maya aide maman. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a lavé la tomate. Elle a posé la cuillère. Elle a apporté le pain. Avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maya s'assoit. Elle croque un morceau de pain. Maman est près d'elle.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.CUI.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Maya reste avec maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Maya aide maman. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Maya a lavé la tomate. Elle a posé la cuillère. Elle a apporté le pain. Avec maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Maya s'assoit. Elle croque un morceau de pain. Maman est près d'elle.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.CUI.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maya aide maman</t>
+          <t>Le goûter jaune de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut un goûter jaune. La fourchette glisse. Elles rient et recommencent. La banane devient un nuage. Elles goûtent près du carreau.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Maya entre dans la cuisine. Maman est là. Je veux aider. Maman sourit. Tu fais une tâche sûre, avec un adulte. Maya ouvre l'eau. Elle lave une tomate. L'eau est froide. La tomate est lisse. Maya pose la tomate. Ensuite, elle prend une cuillère. Elle pose la cuillère près de l'assiette. Puis Maya va au pain. Elle apporte le pain à table. Merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Maya reste avec maman.</t>
+          <t>Un rayon jaune traverse le carreau. La table a un carré de soleil. Une banane attend dans le bol. Elle sent le sucre mûr. Tu as vu le rayon, Sarah ? Il est jaune. Oui. Comme la banane. En ce moment, Sarah a faim. Je veux le goûter jaune. On l'écrase ensemble ? Oui. Je peux aider ? Oui, avec moi. Maman pose une fourchette. Sarah tient le bol des deux mains. La banane est molle et tiède. Sarah appuie un peu. La fourchette glisse. Elle fait un petit clac. Elle part ! On la reprend ? Oui. Elles rient toutes les deux. Sarah reprend la fourchette. Elle appuie plus doucement. La banane s'écrase, tout jaune. Ça devient un nuage. Oui. Tu aides bien. Le bol sent le fruit mûr. Un peu de jaune reste au bord. Sarah tourne encore la fourchette. C'est assez mou ? Oui. Merci, Sarah. Maman pose deux petites cuillères. Sarah apporte le bol à table. Le rayon touche encore le bois. On goûte ? Oui. Sarah prend une cuillerée. C'est doux et un peu sucré. C'est jaune. C'est ton goûter. Une mouche passe près du carreau. Sarah souffle tout doux. Tu as encore faim ? Encore un peu. Elles mangent près de la fenêtre. Le bois de la table est chaud. Sarah lèche un peu de jaune. Tu as écrasé avec moi. La fourchette a glissé. Puis on a recommencé. Le bol se vide tout doux. Le rayon glisse vers le mur. Il est bon, le jaune. Oui. Sarah pose sa cuillère. Elle a un point jaune au nez. Un petit nuage, là. Sur mon nez ? Oui. Sarah rit encore. Maman essuie le point jaune.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;C'est le matin. Maya entre dans la cuisine. Maman est là. Maya dit : je veux aider. Maman sourit. Maman dit : tu fais une &lt;emphasis level="moderate"&gt;tâche&lt;/emphasis&gt; sûre, avec un adulte. Maya ouvre l'eau. Elle lave une tomate. L'eau est froide. La tomate est lisse. Maya pose la tomate. Ensuite, elle prend une cuillère. Elle pose la cuillère près de l'assiette. Puis Maya va au pain. Elle apporte le pain à table. Maman dit : merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Maya reste avec maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon jaune traverse le carreau. La table a un carré de soleil. Une banane attend dans le bol. Elle sent le sucre mûr. Tu as vu le rayon, Sarah ? Il est jaune. Oui. Comme la banane. En ce moment, Sarah a faim. Je veux le goûter jaune. On l'écrase ensemble ? Oui. Je peux aider ? Oui, avec moi. Maman pose une fourchette. Sarah tient le bol des deux mains. La banane est molle et tiède. Sarah appuie un peu. La fourchette glisse. Elle fait un petit clac. Elle part ! On la reprend ? Oui. Elles rient toutes les deux. Sarah reprend la fourchette. Elle appuie plus doucement. La banane s'écrase, tout jaune. Ça devient un nuage. Oui. Tu aides bien. Le bol sent le fruit mûr. Un peu de jaune reste au bord. Sarah tourne encore la fourchette. C'est assez mou ? Oui. Merci, Sarah. Maman pose deux petites cuillères. Sarah apporte le bol à table. Le rayon touche encore le bois. On goûte ? Oui. Sarah prend une cuillerée. C'est doux et un peu sucré. C'est jaune. C'est ton goûter. Une mouche passe près du carreau. Sarah souffle tout doux. Tu as encore faim ? Encore un peu. Elles mangent près de la fenêtre. Le bois de la table est chaud. Sarah lèche un peu de jaune. Tu as écrasé avec moi. La fourchette a glissé. Puis on a recommencé. Le bol se vide tout doux. Le rayon glisse vers le mur. Il est bon, le jaune. Oui. Sarah pose sa cuillère. Elle a un point jaune au nez. Un petit nuage, là. Sur mon nez ? Oui. Sarah rit encore. Maman essuie le point jaune.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,74 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Maya entre dans la cuisine. Maman est là.
-enfant-f|Je veux aider. Maman sourit.
-maman|Tu fais une tâche sûre, avec un adulte.
-narrateur|Maya ouvre l'eau. Elle lave une tomate. L'eau est froide. La tomate est lisse. Maya pose la tomate. Ensuite, elle prend une cuillère. Elle pose la cuillère près de l'assiette. Puis Maya va au pain. Elle apporte le pain à table.
-maman|Merci. Laver. Poser. Apporter. Ce sont des tâches sûres.
-narrateur|Maya reste avec maman.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un rayon jaune traverse le carreau.
+narrateur|La table a un carré de soleil.
+narrateur|Une banane attend dans le bol.
+narrateur|Elle sent le sucre mûr.
+maman|Tu as vu le rayon, Sarah ?
+enfant-f|Il est jaune.
+maman|Oui.
+maman|Comme la banane.
+narrateur|En ce moment, Sarah a faim.
+enfant-f|Je veux le goûter jaune.
+maman|On l'écrase ensemble ?
+enfant-f|Oui.
+enfant-f|Je peux aider ?
+maman|Oui, avec moi.
+narrateur|Maman pose une fourchette.
+narrateur|Sarah tient le bol des deux mains.
+narrateur|La banane est molle et tiède.
+narrateur|Sarah appuie un peu.
+narrateur|La fourchette glisse.
+narrateur|Elle fait un petit clac.
+enfant-f|Elle part !
+maman|On la reprend ?
+enfant-f|Oui.
+narrateur|Elles rient toutes les deux.
+narrateur|Sarah reprend la fourchette.
+narrateur|Elle appuie plus doucement.
+narrateur|La banane s'écrase, tout jaune.
+enfant-f|Ça devient un nuage.
+maman|Oui.
+maman|Tu aides bien.
+narrateur|Le bol sent le fruit mûr.
+narrateur|Un peu de jaune reste au bord.
+narrateur|Sarah tourne encore la fourchette.
+maman|C'est assez mou ?
+enfant-f|Oui.
+maman|Merci, Sarah.
+narrateur|Maman pose deux petites cuillères.
+narrateur|Sarah apporte le bol à table.
+narrateur|Le rayon touche encore le bois.
+enfant-f|On goûte ?
+maman|Oui.
+narrateur|Sarah prend une cuillerée.
+narrateur|C'est doux et un peu sucré.
+enfant-f|C'est jaune.
+maman|C'est ton goûter.
+narrateur|Une mouche passe près du carreau.
+narrateur|Sarah souffle tout doux.
+maman|Tu as encore faim ?
+enfant-f|Encore un peu.
+narrateur|Elles mangent près de la fenêtre.
+narrateur|Le bois de la table est chaud.
+narrateur|Sarah lèche un peu de jaune.
+maman|Tu as écrasé avec moi.
+enfant-f|La fourchette a glissé.
+maman|Puis on a recommencé.
+narrateur|Le bol se vide tout doux.
+narrateur|Le rayon glisse vers le mur.
+enfant-f|Il est bon, le jaune.
+maman|Oui.
+narrateur|Sarah pose sa cuillère.
+narrateur|Elle a un point jaune au nez.
+maman|Un petit nuage, là.
+enfant-f|Sur mon nez ?
+maman|Oui.
+narrateur|Sarah rit encore.
+narrateur|Maman essuie le point jaune.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1416,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Maya aide maman. Que fait-elle ?</t>
+          <t>Sarah veut le goûter jaune. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maya aide maman. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah veut le goûter jaune. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1360,12 +1431,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>aider</t>
+          <t>écraser</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>aider | laver | apporter | avec maman</t>
+          <t>écraser | elle écrase | la banane | elle aide | avec maman | le goûter</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1451,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle lave la tomate. Que fait Maya ?</t>
+          <t>Sarah aide maman. Que fait-elle ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1429,7 +1500,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1501,10 +1572,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Maya aide maman. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah veut le goûter jaune.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1529,12 +1600,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya a lavé la tomate. Elle a posé la cuillère. Elle a apporté le pain. Avec maman.</t>
+          <t>Sarah a écrasé la banane. La fourchette a glissé. Elles ont ri, puis repris. Tu as aidé, Sarah. Le goûter est jaune. Oui. Le bol sent encore le fruit. Le rayon touche la table.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maya a lavé la tomate. Elle a posé la cuillère. Elle a apporté le pain. &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a écrasé la banane. La fourchette a glissé. Elles ont ri, puis repris. Tu as aidé, Sarah. Le goûter est jaune. Oui. Le bol sent encore le fruit. Le rayon touche la table.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1590,14 +1661,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1673,10 +1744,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maya a lavé la tomate. Elle a posé la cuillère. Elle a apporté le pain. Avec maman.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah a écrasé la banane.
+narrateur|La fourchette a glissé.
+narrateur|Elles ont ri, puis repris.
+maman|Tu as aidé, Sarah.
+enfant-f|Le goûter est jaune.
+maman|Oui.
+narrateur|Le bol sent encore le fruit.
+narrateur|Le rayon touche la table.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1701,12 +1778,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maya s'assoit. Elle croque un morceau de pain. Maman est près d'elle.</t>
+          <t>Sarah apporte le bol vide. On le pose près de l'évier ? Oui. L'eau chante un peu. Sarah rince sa cuillère. Merci pour le goûter. Il était jaune. Oui, tout doux. Le carreau a encore du soleil. La table garde un carré chaud.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maya s'assoit. Elle croque un morceau de pain. Maman est près d'elle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah apporte le bol vide. On le pose près de l'évier ? Oui. L'eau chante un peu. Sarah rince sa cuillère. Merci pour le goûter. Il était jaune. Oui, tout doux. Le carreau a encore du soleil. La table garde un carré chaud.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1762,14 +1839,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1837,10 +1914,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maya s'assoit. Elle croque un morceau de pain. Maman est près d'elle.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah apporte le bol vide.
+maman|On le pose près de l'évier ?
+enfant-f|Oui.
+narrateur|L'eau chante un peu.
+narrateur|Sarah rince sa cuillère.
+maman|Merci pour le goûter.
+enfant-f|Il était jaune.
+maman|Oui, tout doux.
+narrateur|Le carreau a encore du soleil.
+narrateur|La table garde un carré chaud.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1865,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah s'assoit près du carreau. Le nuage était bon. Oui. Un peu de jaune brille au bol. Le goûter jaune sent encore le fruit.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah s'assoit près du carreau. Le nuage était bon. Oui. Un peu de jaune brille au bol. Le goûter jaune sent encore le fruit.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1926,14 +2011,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2005,10 +2090,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sarah s'assoit près du carreau.
+enfant-f|Le nuage était bon.
+maman|Oui.
+narrateur|Un peu de jaune brille au bol.
+narrateur|Le goûter jaune sent encore le fruit.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2027,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2153,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.CUI.001-01.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine l'après-midi, rayon sur la table</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maya, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
